--- a/registration_forms/041_virtual_card_class_registration--registration_forms.xlsx
+++ b/registration_forms/041_virtual_card_class_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -623,8 +623,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,12 +652,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'class1',_'label':_'class_1'}</t>
+          <t>class_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'class1', 'label': 'Class 1'}</t>
+          <t>Class 1</t>
         </is>
       </c>
     </row>
@@ -669,12 +669,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'class2',_'label':_'class_2'}</t>
+          <t>class_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'class2', 'label': 'Class 2'}</t>
+          <t>Class 2</t>
         </is>
       </c>
     </row>
@@ -686,12 +686,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'class3',_'label':_'class_3'}</t>
+          <t>class_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'class3', 'label': 'Class 3'}</t>
+          <t>Class 3</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'agree',_'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'agree', 'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'decline',_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'decline', 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'undetermined',_'label':_'undetermined'}</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'undetermined', 'label': 'Undetermined'}</t>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
